--- a/7_DE_Genes/DE_Genes_Summary.xlsx
+++ b/7_DE_Genes/DE_Genes_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cassiopea/Documents/GitHub/2024_Leukoma_RNA-Seq/7_DE_Genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A6A6943-71A6-614D-AD6E-DAB3760A3117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C416AF-53E2-BD45-AF8D-C16F3857BCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12460" yWindow="1960" windowWidth="27640" windowHeight="16940" xr2:uid="{AB0BFB6F-2D6E-BC4A-A2E4-4C96726E357E}"/>
+    <workbookView xWindow="4100" yWindow="740" windowWidth="35720" windowHeight="16940" xr2:uid="{AB0BFB6F-2D6E-BC4A-A2E4-4C96726E357E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="705">
   <si>
     <t>Cluster-101559.0</t>
   </si>
@@ -1961,27 +1961,12 @@
     <t>T1_TRINITY_DN70841_c0_g1_i1</t>
   </si>
   <si>
-    <t>DE in Multiple Comparisons?</t>
-  </si>
-  <si>
     <t>[EA_v_EASH] and [C_v_EA]</t>
   </si>
   <si>
-    <t>[C_v_EASH] and [C_v_EA]</t>
-  </si>
-  <si>
-    <t>[EA_v_EASH] and [C_v_EASH]</t>
-  </si>
-  <si>
     <t>[EA_v_SH] and [C_v_EA]</t>
   </si>
   <si>
-    <t>[EA_v_SH] and [EA_v_EASH]</t>
-  </si>
-  <si>
-    <t>Protein?</t>
-  </si>
-  <si>
     <t>T1_TRINITY_DN11475_c1_g1_i7.p1</t>
   </si>
   <si>
@@ -2003,9 +1988,6 @@
     <t>T1_TRINITY_DN3041_c0_g1_i7.p1</t>
   </si>
   <si>
-    <t>T1_TRINITY_DN5378_c0_g1_i1.p1</t>
-  </si>
-  <si>
     <t>T1_TRINITY_DN5831_c1_g1_i9.p1</t>
   </si>
   <si>
@@ -2021,7 +2003,7 @@
     <t>T1_TRINITY_DN97506_c0_g1_i2.p1</t>
   </si>
   <si>
-    <t>T2_TRINITY_DN12954_c0_g1_i11.p1</t>
+    <t>T2_TRINITY_DN12954_c0_g1_i11.p2</t>
   </si>
   <si>
     <t>T2_TRINITY_DN13977_c0_g1_i6.p1</t>
@@ -2054,9 +2036,6 @@
     <t>T2_TRINITY_DN541_c3_g1_i2.p1</t>
   </si>
   <si>
-    <t>T2_TRINITY_DN56795_c0_g1_i8.p1</t>
-  </si>
-  <si>
     <t>T2_TRINITY_DN6213_c7_g1_i3.p1</t>
   </si>
   <si>
@@ -2082,6 +2061,96 @@
   </si>
   <si>
     <t>Corset-Gene_ID</t>
+  </si>
+  <si>
+    <t>prot_id</t>
+  </si>
+  <si>
+    <t>sprot_Top_BLASTP_hit</t>
+  </si>
+  <si>
+    <t>Pfam</t>
+  </si>
+  <si>
+    <t>UB2J2_HUMAN^UB2J2_HUMAN^Q:2-236,H:4-258^63.5%ID^E:9.03e-107^RecName: Full=Ubiquitin-conjugating enzyme E2 J2;^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Mammalia; Eutheria; Euarchontoglires; Primates; Haplorrhini; Catarrhini; Hominidae; Homo</t>
+  </si>
+  <si>
+    <t>PF00179.30^UQ_con^NULL^14-125^E:3e-19</t>
+  </si>
+  <si>
+    <t>PIMT_DANRE^PIMT_DANRE^Q:36-260,H:1-223^65.8%ID^E:2.25e-103^RecName: Full=Protein-L-isoaspartate(D-aspartate) O-methyltransferase {ECO:0000250|UniProtKB:P23506};^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Actinopterygii; Neopterygii; Teleostei; Ostariophysi; Cypriniformes; Danionidae; Danioninae; Danio</t>
+  </si>
+  <si>
+    <t>PF01135.23^PCMT^NULL^44-257^E:2.6e-79`PF01209.22^Ubie_methyltran^NULL^110-199^E:0.0011</t>
+  </si>
+  <si>
+    <t>R213A_DANRE^R213A_DANRE^Q:47-1809,H:3502-5207^26.7%ID^E:1.94e-158^RecName: Full=E3 ubiquitin-protein ligase rnf213-alpha {ECO:0000305};^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Actinopterygii; Neopterygii; Teleostei; Ostariophysi; Cypriniformes; Danionidae; Danioninae; Danio</t>
+  </si>
+  <si>
+    <t>PF20173.2^ZnF_RZ-type^NULL^1082-1128^E:1.3e-16</t>
+  </si>
+  <si>
+    <t>T1_TRINITY_DN5378_c0_g1_i1.p2</t>
+  </si>
+  <si>
+    <t>DYM_DROME^DYM_DROME^Q:30-175,H:180-325^36.8%ID^E:3.18e-14^RecName: Full=Dymeclin;^Eukaryota; Metazoa; Ecdysozoa; Arthropoda; Hexapoda; Insecta; Pterygota; Neoptera; Endopterygota; Diptera; Brachycera; Muscomorpha; Ephydroidea; Drosophilidae; Drosophila; Sophophora</t>
+  </si>
+  <si>
+    <t>PF09742.13^Dymeclin^NULL^25-179^E:1.9e-30</t>
+  </si>
+  <si>
+    <t>DYM_DROME^DYM_DROME^Q:30-100,H:180-247^49.3%ID^E:1.04e-09^RecName: Full=Dymeclin;^Eukaryota; Metazoa; Ecdysozoa; Arthropoda; Hexapoda; Insecta; Pterygota; Neoptera; Endopterygota; Diptera; Brachycera; Muscomorpha; Ephydroidea; Drosophilidae; Drosophila; Sophophora</t>
+  </si>
+  <si>
+    <t>PF09742.13^Dymeclin^NULL^24-110^E:4.7e-20</t>
+  </si>
+  <si>
+    <t>ARFRP_BOVIN^ARFRP_BOVIN^Q:1-202,H:1-201^64.9%ID^E:3.28e-94^RecName: Full=ADP-ribosylation factor-related protein 1;^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Mammalia; Eutheria; Laurasiatheria; Artiodactyla; Ruminantia; Pecora; Bovidae; Bovinae; Bos</t>
+  </si>
+  <si>
+    <t>PF00025.25^Arf^NULL^10-185^E:4.7e-47`PF09439.14^SRPRB^NULL^18-140^E:3.4e-06`PF04670.16^Gtr1_RagA^NULL^20-138^E:7e-07`PF01926.27^MMR_HSR1^NULL^20-135^E:5.4e-06`PF00071.26^Ras^NULL^20-187^E:3.9e-12`PF08477.17^Roc^NULL^20-137^E:7.8e-12</t>
+  </si>
+  <si>
+    <t>KLRE1_RAT^KLRE1_RAT^Q:162-287,H:113-226^25.6%ID^E:1.54e-06^RecName: Full=Killer cell lectin-like receptor subfamily E member 1 {ECO:0000303|PubMed:12782717};^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Mammalia; Eutheria; Euarchontoglires; Glires; Rodentia; Myomorpha; Muroidea; Muridae; Murinae; Rattus</t>
+  </si>
+  <si>
+    <t>PF00059.25^Lectin_C^NULL^182-287^E:5.6e-17</t>
+  </si>
+  <si>
+    <t>PSA7_CARAU^PSA7_CARAU^Q:3-104,H:1-100^75.5%ID^E:2.06e-45^RecName: Full=Proteasome subunit alpha type-7;^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Actinopterygii; Neopterygii; Teleostei; Ostariophysi; Cypriniformes; Cyprinidae; Cyprininae; Carassius</t>
+  </si>
+  <si>
+    <t>PF10584.13^Proteasome_A_N^NULL^7-29^E:2.1e-14`PF00227.30^Proteasome^NULL^30-94^E:5.9e-15</t>
+  </si>
+  <si>
+    <t>RBM39_PONAB^RBM39_PONAB^Q:1-101,H:182-281^70.3%ID^E:3.3e-38^RecName: Full=RNA-binding protein 39;^Eukaryota; Metazoa; Chordata; Craniata; Vertebrata; Euteleostomi; Mammalia; Eutheria; Euarchontoglires; Primates; Haplorrhini; Catarrhini; Hominidae; Pongo</t>
+  </si>
+  <si>
+    <t>PF00076.26^RRM_1^NULL^72-104^E:6.7e-07</t>
+  </si>
+  <si>
+    <t>PF12773.11^DZR^NULL^46-94^E:4.5e-06</t>
+  </si>
+  <si>
+    <t>T2_TRINITY_DN56795_c0_g1_i8.p2</t>
+  </si>
+  <si>
+    <t>PF00910.26^RNA_helicase^NULL^56-99^E:0.0013</t>
+  </si>
+  <si>
+    <t>DE in Multiple Comparisons?.</t>
+  </si>
+  <si>
+    <t>[C_v_EASH] and [C_v_EA].</t>
+  </si>
+  <si>
+    <t>[EA_v_SH] and [EA_v_EASH].</t>
+  </si>
+  <si>
+    <t>[EA_v_EASH] and [C_v_EASH].</t>
+  </si>
+  <si>
+    <t>[EA_v_SH] and [C_v_EA].</t>
   </si>
 </sst>
 </file>
@@ -2468,35 +2537,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2E4391-38EA-4A41-8F0F-5324197F3D9F}">
-  <dimension ref="A1:E334"/>
+  <dimension ref="A1:G334"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="64.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="229.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>700</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2506,10 +2583,20 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2519,10 +2606,20 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2532,10 +2629,20 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2545,10 +2652,20 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -2558,12 +2675,20 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E6" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -2573,10 +2698,20 @@
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -2586,10 +2721,20 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -2599,10 +2744,20 @@
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -2612,10 +2767,20 @@
       <c r="C10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2625,10 +2790,20 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2638,10 +2813,20 @@
       <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2651,10 +2836,20 @@
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -2664,10 +2859,20 @@
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -2677,10 +2882,20 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -2690,10 +2905,20 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,10 +2928,20 @@
       <c r="C17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -2716,10 +2951,20 @@
       <c r="C18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
@@ -2729,10 +2974,20 @@
       <c r="C19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -2742,10 +2997,20 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -2755,10 +3020,20 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
@@ -2768,10 +3043,20 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
@@ -2781,10 +3066,20 @@
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -2794,10 +3089,20 @@
       <c r="C24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,11 +3113,19 @@
         <v>2</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>701</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
@@ -2822,10 +3135,20 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -2835,10 +3158,20 @@
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>49</v>
       </c>
@@ -2848,12 +3181,20 @@
       <c r="C28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E28" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>666</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
@@ -2863,10 +3204,20 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
@@ -2876,10 +3227,20 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
@@ -2889,10 +3250,20 @@
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,10 +3273,20 @@
       <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,10 +3296,20 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
@@ -2928,10 +3319,20 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>61</v>
       </c>
@@ -2941,10 +3342,20 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>64</v>
       </c>
@@ -2954,10 +3365,20 @@
       <c r="C36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>67</v>
       </c>
@@ -2967,10 +3388,20 @@
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>69</v>
       </c>
@@ -2980,10 +3411,20 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
@@ -2993,10 +3434,20 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>73</v>
       </c>
@@ -3006,12 +3457,20 @@
       <c r="C40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E40" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>665</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>76</v>
       </c>
@@ -3021,10 +3480,20 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>78</v>
       </c>
@@ -3034,10 +3503,20 @@
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>80</v>
       </c>
@@ -3047,10 +3526,20 @@
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>80</v>
       </c>
@@ -3060,10 +3549,20 @@
       <c r="C44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>83</v>
       </c>
@@ -3073,10 +3572,20 @@
       <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>85</v>
       </c>
@@ -3086,10 +3595,20 @@
       <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>87</v>
       </c>
@@ -3099,10 +3618,20 @@
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>89</v>
       </c>
@@ -3112,10 +3641,20 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>91</v>
       </c>
@@ -3125,10 +3664,20 @@
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>93</v>
       </c>
@@ -3138,10 +3687,20 @@
       <c r="C50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>95</v>
       </c>
@@ -3151,10 +3710,20 @@
       <c r="C51" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>97</v>
       </c>
@@ -3164,10 +3733,20 @@
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>99</v>
       </c>
@@ -3177,10 +3756,20 @@
       <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>101</v>
       </c>
@@ -3190,10 +3779,20 @@
       <c r="C54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>103</v>
       </c>
@@ -3203,10 +3802,20 @@
       <c r="C55" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>105</v>
       </c>
@@ -3216,10 +3825,20 @@
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>107</v>
       </c>
@@ -3229,10 +3848,20 @@
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>109</v>
       </c>
@@ -3242,10 +3871,20 @@
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>111</v>
       </c>
@@ -3255,10 +3894,20 @@
       <c r="C59" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>111</v>
       </c>
@@ -3268,10 +3917,20 @@
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>111</v>
       </c>
@@ -3281,10 +3940,20 @@
       <c r="C61" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>115</v>
       </c>
@@ -3294,10 +3963,20 @@
       <c r="C62" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>117</v>
       </c>
@@ -3307,12 +3986,20 @@
       <c r="C63" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E63" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>120</v>
       </c>
@@ -3322,10 +4009,20 @@
       <c r="C64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>122</v>
       </c>
@@ -3335,10 +4032,20 @@
       <c r="C65" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>122</v>
       </c>
@@ -3348,10 +4055,20 @@
       <c r="C66" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>125</v>
       </c>
@@ -3361,10 +4078,20 @@
       <c r="C67" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>127</v>
       </c>
@@ -3374,12 +4101,20 @@
       <c r="C68" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E68" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>669</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>129</v>
       </c>
@@ -3389,10 +4124,20 @@
       <c r="C69" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>131</v>
       </c>
@@ -3402,12 +4147,20 @@
       <c r="C70" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E70" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>133</v>
       </c>
@@ -3417,10 +4170,20 @@
       <c r="C71" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>136</v>
       </c>
@@ -3430,12 +4193,20 @@
       <c r="C72" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E72" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>138</v>
       </c>
@@ -3445,10 +4216,20 @@
       <c r="C73" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>140</v>
       </c>
@@ -3458,10 +4239,20 @@
       <c r="C74" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>142</v>
       </c>
@@ -3471,10 +4262,20 @@
       <c r="C75" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>145</v>
       </c>
@@ -3484,10 +4285,20 @@
       <c r="C76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>147</v>
       </c>
@@ -3497,10 +4308,20 @@
       <c r="C77" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>149</v>
       </c>
@@ -3510,12 +4331,20 @@
       <c r="C78" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D78" s="3"/>
+      <c r="D78" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E78" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>152</v>
       </c>
@@ -3525,12 +4354,20 @@
       <c r="C79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D79" s="3"/>
+      <c r="D79" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E79" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+        <v>661</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>154</v>
       </c>
@@ -3540,12 +4377,20 @@
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D80" s="3"/>
+      <c r="D80" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E80" s="3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>156</v>
       </c>
@@ -3555,10 +4400,20 @@
       <c r="C81" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>158</v>
       </c>
@@ -3568,10 +4423,20 @@
       <c r="C82" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>160</v>
       </c>
@@ -3581,12 +4446,20 @@
       <c r="C83" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D83" s="3"/>
+      <c r="D83" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E83" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+        <v>655</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>162</v>
       </c>
@@ -3596,10 +4469,20 @@
       <c r="C84" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>164</v>
       </c>
@@ -3609,10 +4492,20 @@
       <c r="C85" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>166</v>
       </c>
@@ -3622,10 +4515,20 @@
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>168</v>
       </c>
@@ -3635,12 +4538,20 @@
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="3"/>
+      <c r="D87" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E87" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>170</v>
       </c>
@@ -3650,10 +4561,20 @@
       <c r="C88" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>173</v>
       </c>
@@ -3663,10 +4584,20 @@
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>175</v>
       </c>
@@ -3676,10 +4607,20 @@
       <c r="C90" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>175</v>
       </c>
@@ -3689,10 +4630,20 @@
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>178</v>
       </c>
@@ -3702,10 +4653,20 @@
       <c r="C92" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D92" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>180</v>
       </c>
@@ -3716,11 +4677,19 @@
         <v>2</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>182</v>
       </c>
@@ -3730,12 +4699,20 @@
       <c r="C94" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D94" s="3"/>
+      <c r="D94" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E94" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+        <v>648</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>185</v>
       </c>
@@ -3745,10 +4722,20 @@
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>187</v>
       </c>
@@ -3758,10 +4745,20 @@
       <c r="C96" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>189</v>
       </c>
@@ -3771,10 +4768,20 @@
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>191</v>
       </c>
@@ -3784,12 +4791,20 @@
       <c r="C98" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D98" s="3"/>
+      <c r="D98" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E98" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+        <v>643</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>191</v>
       </c>
@@ -3799,10 +4814,20 @@
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>194</v>
       </c>
@@ -3812,10 +4837,20 @@
       <c r="C100" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>194</v>
       </c>
@@ -3825,10 +4860,20 @@
       <c r="C101" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>197</v>
       </c>
@@ -3838,10 +4883,20 @@
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>199</v>
       </c>
@@ -3851,10 +4906,20 @@
       <c r="C103" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>201</v>
       </c>
@@ -3864,10 +4929,20 @@
       <c r="C104" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>201</v>
       </c>
@@ -3877,10 +4952,20 @@
       <c r="C105" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>204</v>
       </c>
@@ -3890,10 +4975,20 @@
       <c r="C106" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>206</v>
       </c>
@@ -3903,10 +4998,20 @@
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>206</v>
       </c>
@@ -3916,10 +5021,20 @@
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>209</v>
       </c>
@@ -3929,10 +5044,20 @@
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>211</v>
       </c>
@@ -3942,10 +5067,20 @@
       <c r="C110" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D110" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>214</v>
       </c>
@@ -3955,10 +5090,20 @@
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D111" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>216</v>
       </c>
@@ -3968,10 +5113,20 @@
       <c r="C112" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D112" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>218</v>
       </c>
@@ -3981,10 +5136,20 @@
       <c r="C113" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>220</v>
       </c>
@@ -3995,11 +5160,19 @@
         <v>2</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E114" s="3"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>222</v>
       </c>
@@ -4009,12 +5182,20 @@
       <c r="C115" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D115" s="3"/>
+      <c r="D115" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E115" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+        <v>645</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>222</v>
       </c>
@@ -4024,12 +5205,20 @@
       <c r="C116" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D116" s="3"/>
+      <c r="D116" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E116" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+        <v>662</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>225</v>
       </c>
@@ -4039,10 +5228,20 @@
       <c r="C117" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D117" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>227</v>
       </c>
@@ -4052,10 +5251,20 @@
       <c r="C118" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D118" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>230</v>
       </c>
@@ -4065,10 +5274,20 @@
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>232</v>
       </c>
@@ -4078,10 +5297,20 @@
       <c r="C120" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D120" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>234</v>
       </c>
@@ -4091,10 +5320,20 @@
       <c r="C121" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>236</v>
       </c>
@@ -4104,10 +5343,20 @@
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D122" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>238</v>
       </c>
@@ -4117,10 +5366,20 @@
       <c r="C123" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>240</v>
       </c>
@@ -4130,10 +5389,20 @@
       <c r="C124" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>242</v>
       </c>
@@ -4143,10 +5412,20 @@
       <c r="C125" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D125" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>242</v>
       </c>
@@ -4156,10 +5435,20 @@
       <c r="C126" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D126" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>245</v>
       </c>
@@ -4169,10 +5458,20 @@
       <c r="C127" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>247</v>
       </c>
@@ -4182,10 +5481,20 @@
       <c r="C128" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D128" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>249</v>
       </c>
@@ -4195,10 +5504,20 @@
       <c r="C129" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D129" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>249</v>
       </c>
@@ -4208,10 +5527,20 @@
       <c r="C130" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D130" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>252</v>
       </c>
@@ -4221,10 +5550,20 @@
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D131" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>254</v>
       </c>
@@ -4234,10 +5573,20 @@
       <c r="C132" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>256</v>
       </c>
@@ -4247,12 +5596,20 @@
       <c r="C133" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D133" s="3"/>
+      <c r="D133" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E133" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+        <v>698</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>258</v>
       </c>
@@ -4262,10 +5619,20 @@
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D134" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>260</v>
       </c>
@@ -4275,10 +5642,20 @@
       <c r="C135" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D135" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>262</v>
       </c>
@@ -4288,10 +5665,20 @@
       <c r="C136" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D136" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>262</v>
       </c>
@@ -4301,10 +5688,20 @@
       <c r="C137" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D137" s="3"/>
-      <c r="E137" s="3"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D137" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>265</v>
       </c>
@@ -4314,10 +5711,20 @@
       <c r="C138" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D138" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>265</v>
       </c>
@@ -4327,10 +5734,20 @@
       <c r="C139" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D139" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>268</v>
       </c>
@@ -4340,10 +5757,20 @@
       <c r="C140" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D140" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>270</v>
       </c>
@@ -4353,10 +5780,20 @@
       <c r="C141" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D141" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>272</v>
       </c>
@@ -4366,10 +5803,20 @@
       <c r="C142" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D142" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>274</v>
       </c>
@@ -4379,10 +5826,20 @@
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D143" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>276</v>
       </c>
@@ -4392,10 +5849,20 @@
       <c r="C144" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>276</v>
       </c>
@@ -4405,12 +5872,20 @@
       <c r="C145" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D145" s="3"/>
+      <c r="D145" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E145" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+        <v>656</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>279</v>
       </c>
@@ -4420,10 +5895,20 @@
       <c r="C146" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D146" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>281</v>
       </c>
@@ -4433,10 +5918,20 @@
       <c r="C147" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D147" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>283</v>
       </c>
@@ -4446,12 +5941,20 @@
       <c r="C148" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D148" s="3"/>
+      <c r="D148" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E148" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>283</v>
       </c>
@@ -4461,10 +5964,20 @@
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>286</v>
       </c>
@@ -4474,12 +5987,20 @@
       <c r="C150" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D150" s="3"/>
+      <c r="D150" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E150" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+        <v>664</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>288</v>
       </c>
@@ -4489,10 +6010,20 @@
       <c r="C151" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>290</v>
       </c>
@@ -4502,12 +6033,20 @@
       <c r="C152" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D152" s="3"/>
+      <c r="D152" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E152" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>293</v>
       </c>
@@ -4517,10 +6056,20 @@
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D153" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>295</v>
       </c>
@@ -4530,10 +6079,20 @@
       <c r="C154" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D154" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>297</v>
       </c>
@@ -4544,11 +6103,19 @@
         <v>2</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+        <v>703</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>299</v>
       </c>
@@ -4559,11 +6126,19 @@
         <v>2</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>301</v>
       </c>
@@ -4573,12 +6148,20 @@
       <c r="C157" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D157" s="3"/>
+      <c r="D157" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E157" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+        <v>654</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>304</v>
       </c>
@@ -4588,10 +6171,20 @@
       <c r="C158" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D158" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>306</v>
       </c>
@@ -4601,10 +6194,20 @@
       <c r="C159" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D159" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>308</v>
       </c>
@@ -4614,10 +6217,20 @@
       <c r="C160" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D160" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>310</v>
       </c>
@@ -4627,10 +6240,20 @@
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D161" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>312</v>
       </c>
@@ -4640,10 +6263,20 @@
       <c r="C162" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D162" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>314</v>
       </c>
@@ -4653,10 +6286,20 @@
       <c r="C163" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D163" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>316</v>
       </c>
@@ -4666,10 +6309,20 @@
       <c r="C164" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D164" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>318</v>
       </c>
@@ -4680,11 +6333,19 @@
         <v>2</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>320</v>
       </c>
@@ -4694,10 +6355,20 @@
       <c r="C166" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D166" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>322</v>
       </c>
@@ -4707,10 +6378,20 @@
       <c r="C167" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>324</v>
       </c>
@@ -4720,10 +6401,20 @@
       <c r="C168" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D168" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>324</v>
       </c>
@@ -4733,10 +6424,20 @@
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D169" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>327</v>
       </c>
@@ -4746,12 +6447,20 @@
       <c r="C170" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D170" s="3"/>
+      <c r="D170" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E170" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+        <v>670</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>329</v>
       </c>
@@ -4761,10 +6470,20 @@
       <c r="C171" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D171" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>329</v>
       </c>
@@ -4774,10 +6493,20 @@
       <c r="C172" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D172" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>332</v>
       </c>
@@ -4787,12 +6516,20 @@
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D173" s="3"/>
+      <c r="D173" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E173" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+        <v>684</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>332</v>
       </c>
@@ -4802,12 +6539,20 @@
       <c r="C174" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D174" s="3"/>
+      <c r="D174" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E174" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>335</v>
       </c>
@@ -4817,10 +6562,20 @@
       <c r="C175" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D175" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>337</v>
       </c>
@@ -4830,10 +6585,20 @@
       <c r="C176" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D176" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>337</v>
       </c>
@@ -4843,10 +6608,20 @@
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D177" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>341</v>
       </c>
@@ -4856,10 +6631,20 @@
       <c r="C178" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D178" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>343</v>
       </c>
@@ -4869,10 +6654,20 @@
       <c r="C179" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D179" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>345</v>
       </c>
@@ -4882,10 +6677,20 @@
       <c r="C180" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D180" s="3"/>
-      <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D180" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>348</v>
       </c>
@@ -4895,10 +6700,20 @@
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D181" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>348</v>
       </c>
@@ -4908,12 +6723,20 @@
       <c r="C182" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D182" s="3"/>
+      <c r="D182" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E182" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+        <v>671</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>351</v>
       </c>
@@ -4923,10 +6746,20 @@
       <c r="C183" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D183" s="3"/>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D183" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>353</v>
       </c>
@@ -4936,10 +6769,20 @@
       <c r="C184" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D184" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>355</v>
       </c>
@@ -4949,12 +6792,20 @@
       <c r="C185" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D185" s="3"/>
+      <c r="D185" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E185" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+        <v>659</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>358</v>
       </c>
@@ -4964,10 +6815,20 @@
       <c r="C186" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D186" s="3"/>
-      <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D186" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>360</v>
       </c>
@@ -4977,10 +6838,20 @@
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D187" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>362</v>
       </c>
@@ -4990,10 +6861,20 @@
       <c r="C188" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D188" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>364</v>
       </c>
@@ -5003,10 +6884,20 @@
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D189" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>366</v>
       </c>
@@ -5016,10 +6907,20 @@
       <c r="C190" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D190" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>368</v>
       </c>
@@ -5029,10 +6930,20 @@
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D191" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>370</v>
       </c>
@@ -5042,10 +6953,20 @@
       <c r="C192" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="3"/>
-      <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D192" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>372</v>
       </c>
@@ -5055,10 +6976,20 @@
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D193" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>374</v>
       </c>
@@ -5068,10 +6999,20 @@
       <c r="C194" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D194" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>376</v>
       </c>
@@ -5081,10 +7022,20 @@
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D195" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>378</v>
       </c>
@@ -5094,10 +7045,20 @@
       <c r="C196" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D196" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>378</v>
       </c>
@@ -5107,10 +7068,20 @@
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D197" s="3"/>
-      <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D197" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>378</v>
       </c>
@@ -5120,10 +7091,20 @@
       <c r="C198" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D198" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>378</v>
       </c>
@@ -5133,10 +7114,20 @@
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D199" s="3"/>
-      <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D199" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>383</v>
       </c>
@@ -5146,10 +7137,20 @@
       <c r="C200" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D200" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>385</v>
       </c>
@@ -5159,10 +7160,20 @@
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D201" s="3"/>
-      <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D201" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>387</v>
       </c>
@@ -5172,10 +7183,20 @@
       <c r="C202" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D202" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>389</v>
       </c>
@@ -5185,10 +7206,20 @@
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D203" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>391</v>
       </c>
@@ -5198,10 +7229,20 @@
       <c r="C204" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D204" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>391</v>
       </c>
@@ -5211,10 +7252,20 @@
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D205" s="3"/>
-      <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D205" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>394</v>
       </c>
@@ -5224,10 +7275,20 @@
       <c r="C206" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D206" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>396</v>
       </c>
@@ -5237,10 +7298,20 @@
       <c r="C207" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D207" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>398</v>
       </c>
@@ -5250,10 +7321,20 @@
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D208" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>400</v>
       </c>
@@ -5263,10 +7344,20 @@
       <c r="C209" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D209" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>403</v>
       </c>
@@ -5276,10 +7367,20 @@
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D210" s="3"/>
-      <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D210" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>405</v>
       </c>
@@ -5289,10 +7390,20 @@
       <c r="C211" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D211" s="3"/>
-      <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D211" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>407</v>
       </c>
@@ -5302,10 +7413,20 @@
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D212" s="3"/>
-      <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D212" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>409</v>
       </c>
@@ -5315,10 +7436,20 @@
       <c r="C213" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D213" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>411</v>
       </c>
@@ -5328,10 +7459,20 @@
       <c r="C214" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D214" s="3"/>
-      <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D214" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>413</v>
       </c>
@@ -5341,10 +7482,20 @@
       <c r="C215" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D215" s="3"/>
-      <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D215" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>415</v>
       </c>
@@ -5354,10 +7505,20 @@
       <c r="C216" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D216" s="3"/>
-      <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D216" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>417</v>
       </c>
@@ -5367,10 +7528,20 @@
       <c r="C217" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D217" s="3"/>
-      <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D217" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>419</v>
       </c>
@@ -5380,10 +7551,20 @@
       <c r="C218" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D218" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>421</v>
       </c>
@@ -5393,10 +7574,20 @@
       <c r="C219" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D219" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>423</v>
       </c>
@@ -5406,10 +7597,20 @@
       <c r="C220" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D220" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>426</v>
       </c>
@@ -5419,10 +7620,20 @@
       <c r="C221" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D221" s="3"/>
-      <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D221" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>426</v>
       </c>
@@ -5432,10 +7643,20 @@
       <c r="C222" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D222" s="3"/>
-      <c r="E222" s="3"/>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D222" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>429</v>
       </c>
@@ -5445,10 +7666,20 @@
       <c r="C223" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D223" s="3"/>
-      <c r="E223" s="3"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D223" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>431</v>
       </c>
@@ -5458,10 +7689,20 @@
       <c r="C224" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D224" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>433</v>
       </c>
@@ -5471,10 +7712,20 @@
       <c r="C225" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D225" s="3"/>
-      <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D225" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>435</v>
       </c>
@@ -5484,10 +7735,20 @@
       <c r="C226" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D226" s="3"/>
-      <c r="E226" s="3"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D226" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>437</v>
       </c>
@@ -5497,10 +7758,20 @@
       <c r="C227" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D227" s="3"/>
-      <c r="E227" s="3"/>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D227" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>439</v>
       </c>
@@ -5510,10 +7781,20 @@
       <c r="C228" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D228" s="3"/>
-      <c r="E228" s="3"/>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D228" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>441</v>
       </c>
@@ -5523,10 +7804,20 @@
       <c r="C229" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D229" s="3"/>
-      <c r="E229" s="3"/>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D229" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>441</v>
       </c>
@@ -5536,10 +7827,20 @@
       <c r="C230" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D230" s="3"/>
-      <c r="E230" s="3"/>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D230" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>441</v>
       </c>
@@ -5549,10 +7850,20 @@
       <c r="C231" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D231" s="3"/>
-      <c r="E231" s="3"/>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D231" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>445</v>
       </c>
@@ -5562,10 +7873,20 @@
       <c r="C232" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D232" s="3"/>
-      <c r="E232" s="3"/>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D232" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>447</v>
       </c>
@@ -5576,11 +7897,19 @@
         <v>2</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E233" s="3"/>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>449</v>
       </c>
@@ -5590,10 +7919,20 @@
       <c r="C234" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D234" s="3"/>
-      <c r="E234" s="3"/>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D234" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>451</v>
       </c>
@@ -5603,10 +7942,20 @@
       <c r="C235" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D235" s="3"/>
-      <c r="E235" s="3"/>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D235" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>453</v>
       </c>
@@ -5616,10 +7965,20 @@
       <c r="C236" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D236" s="3"/>
-      <c r="E236" s="3"/>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D236" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>455</v>
       </c>
@@ -5629,10 +7988,20 @@
       <c r="C237" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D237" s="3"/>
-      <c r="E237" s="3"/>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D237" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>457</v>
       </c>
@@ -5642,10 +8011,20 @@
       <c r="C238" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D238" s="3"/>
-      <c r="E238" s="3"/>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D238" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>459</v>
       </c>
@@ -5655,10 +8034,20 @@
       <c r="C239" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D239" s="3"/>
-      <c r="E239" s="3"/>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D239" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>461</v>
       </c>
@@ -5668,10 +8057,20 @@
       <c r="C240" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D240" s="3"/>
-      <c r="E240" s="3"/>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D240" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>463</v>
       </c>
@@ -5681,10 +8080,20 @@
       <c r="C241" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D241" s="3"/>
-      <c r="E241" s="3"/>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D241" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>465</v>
       </c>
@@ -5694,10 +8103,20 @@
       <c r="C242" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D242" s="3"/>
-      <c r="E242" s="3"/>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D242" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>467</v>
       </c>
@@ -5707,10 +8126,20 @@
       <c r="C243" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D243" s="3"/>
-      <c r="E243" s="3"/>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D243" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>470</v>
       </c>
@@ -5720,10 +8149,20 @@
       <c r="C244" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D244" s="3"/>
-      <c r="E244" s="3"/>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D244" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>472</v>
       </c>
@@ -5733,10 +8172,20 @@
       <c r="C245" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D245" s="3"/>
-      <c r="E245" s="3"/>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D245" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>474</v>
       </c>
@@ -5746,12 +8195,20 @@
       <c r="C246" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D246" s="3"/>
+      <c r="D246" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E246" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>476</v>
       </c>
@@ -5761,10 +8218,20 @@
       <c r="C247" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D247" s="3"/>
-      <c r="E247" s="3"/>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D247" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>476</v>
       </c>
@@ -5774,10 +8241,20 @@
       <c r="C248" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D248" s="3"/>
-      <c r="E248" s="3"/>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D248" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>479</v>
       </c>
@@ -5787,10 +8264,20 @@
       <c r="C249" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D249" s="3"/>
-      <c r="E249" s="3"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D249" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>481</v>
       </c>
@@ -5801,11 +8288,19 @@
         <v>2</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E250" s="3"/>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>483</v>
       </c>
@@ -5815,10 +8310,20 @@
       <c r="C251" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D251" s="3"/>
-      <c r="E251" s="3"/>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D251" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>485</v>
       </c>
@@ -5828,10 +8333,20 @@
       <c r="C252" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D252" s="3"/>
-      <c r="E252" s="3"/>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D252" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>487</v>
       </c>
@@ -5841,10 +8356,20 @@
       <c r="C253" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D253" s="3"/>
-      <c r="E253" s="3"/>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D253" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>490</v>
       </c>
@@ -5854,10 +8379,20 @@
       <c r="C254" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D254" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
         <v>492</v>
       </c>
@@ -5867,10 +8402,20 @@
       <c r="C255" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D255" s="3"/>
-      <c r="E255" s="3"/>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D255" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>494</v>
       </c>
@@ -5880,10 +8425,20 @@
       <c r="C256" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D256" s="3"/>
-      <c r="E256" s="3"/>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D256" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
         <v>494</v>
       </c>
@@ -5893,10 +8448,20 @@
       <c r="C257" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D257" s="3"/>
-      <c r="E257" s="3"/>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D257" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
         <v>494</v>
       </c>
@@ -5906,10 +8471,20 @@
       <c r="C258" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D258" s="3"/>
-      <c r="E258" s="3"/>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D258" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
         <v>498</v>
       </c>
@@ -5919,10 +8494,20 @@
       <c r="C259" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D259" s="3"/>
-      <c r="E259" s="3"/>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D259" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>500</v>
       </c>
@@ -5933,11 +8518,19 @@
         <v>2</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E260" s="3"/>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+        <v>702</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
         <v>502</v>
       </c>
@@ -5947,10 +8540,20 @@
       <c r="C261" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D261" s="3"/>
-      <c r="E261" s="3"/>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D261" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>504</v>
       </c>
@@ -5960,10 +8563,20 @@
       <c r="C262" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D262" s="3"/>
-      <c r="E262" s="3"/>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D262" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>506</v>
       </c>
@@ -5973,10 +8586,20 @@
       <c r="C263" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D263" s="3"/>
-      <c r="E263" s="3"/>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D263" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>508</v>
       </c>
@@ -5986,10 +8609,20 @@
       <c r="C264" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D264" s="3"/>
-      <c r="E264" s="3"/>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D264" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>510</v>
       </c>
@@ -5999,10 +8632,20 @@
       <c r="C265" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D265" s="3"/>
-      <c r="E265" s="3"/>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D265" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
         <v>510</v>
       </c>
@@ -6012,10 +8655,20 @@
       <c r="C266" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D266" s="3"/>
-      <c r="E266" s="3"/>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D266" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
         <v>510</v>
       </c>
@@ -6025,10 +8678,20 @@
       <c r="C267" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D267" s="3"/>
-      <c r="E267" s="3"/>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D267" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
         <v>510</v>
       </c>
@@ -6038,10 +8701,20 @@
       <c r="C268" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D268" s="3"/>
-      <c r="E268" s="3"/>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D268" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>515</v>
       </c>
@@ -6051,10 +8724,20 @@
       <c r="C269" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D269" s="3"/>
-      <c r="E269" s="3"/>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D269" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
         <v>517</v>
       </c>
@@ -6064,10 +8747,20 @@
       <c r="C270" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D270" s="3"/>
-      <c r="E270" s="3"/>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D270" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
         <v>519</v>
       </c>
@@ -6077,10 +8770,20 @@
       <c r="C271" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D271" s="3"/>
-      <c r="E271" s="3"/>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D271" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>521</v>
       </c>
@@ -6090,10 +8793,20 @@
       <c r="C272" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D272" s="3"/>
-      <c r="E272" s="3"/>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D272" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
         <v>523</v>
       </c>
@@ -6103,12 +8816,20 @@
       <c r="C273" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D273" s="3"/>
+      <c r="D273" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E273" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+        <v>651</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
         <v>523</v>
       </c>
@@ -6118,12 +8839,20 @@
       <c r="C274" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D274" s="3"/>
+      <c r="D274" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E274" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
         <v>523</v>
       </c>
@@ -6133,10 +8862,20 @@
       <c r="C275" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D275" s="3"/>
-      <c r="E275" s="3"/>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D275" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>528</v>
       </c>
@@ -6146,10 +8885,20 @@
       <c r="C276" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D276" s="3"/>
-      <c r="E276" s="3"/>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D276" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
         <v>530</v>
       </c>
@@ -6159,10 +8908,20 @@
       <c r="C277" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D277" s="3"/>
-      <c r="E277" s="3"/>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D277" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
         <v>530</v>
       </c>
@@ -6172,10 +8931,20 @@
       <c r="C278" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D278" s="3"/>
-      <c r="E278" s="3"/>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D278" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
         <v>533</v>
       </c>
@@ -6185,10 +8954,20 @@
       <c r="C279" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D279" s="3"/>
-      <c r="E279" s="3"/>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D279" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>535</v>
       </c>
@@ -6198,10 +8977,20 @@
       <c r="C280" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D280" s="3"/>
-      <c r="E280" s="3"/>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D280" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>537</v>
       </c>
@@ -6211,10 +9000,20 @@
       <c r="C281" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D281" s="3"/>
-      <c r="E281" s="3"/>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D281" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>539</v>
       </c>
@@ -6224,10 +9023,20 @@
       <c r="C282" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D282" s="3"/>
-      <c r="E282" s="3"/>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D282" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>539</v>
       </c>
@@ -6237,10 +9046,20 @@
       <c r="C283" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D283" s="3"/>
-      <c r="E283" s="3"/>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D283" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>542</v>
       </c>
@@ -6250,10 +9069,20 @@
       <c r="C284" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D284" s="3"/>
-      <c r="E284" s="3"/>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D284" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>542</v>
       </c>
@@ -6263,10 +9092,20 @@
       <c r="C285" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D285" s="3"/>
-      <c r="E285" s="3"/>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D285" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
         <v>542</v>
       </c>
@@ -6276,10 +9115,20 @@
       <c r="C286" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D286" s="3"/>
-      <c r="E286" s="3"/>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D286" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>546</v>
       </c>
@@ -6289,10 +9138,20 @@
       <c r="C287" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D287" s="3"/>
-      <c r="E287" s="3"/>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D287" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
         <v>548</v>
       </c>
@@ -6302,10 +9161,20 @@
       <c r="C288" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D288" s="3"/>
-      <c r="E288" s="3"/>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D288" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>550</v>
       </c>
@@ -6316,11 +9185,19 @@
         <v>2</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E289" s="3"/>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>552</v>
       </c>
@@ -6330,12 +9207,20 @@
       <c r="C290" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D290" s="3"/>
+      <c r="D290" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="E290" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
         <v>554</v>
       </c>
@@ -6345,10 +9230,20 @@
       <c r="C291" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D291" s="3"/>
-      <c r="E291" s="3"/>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D291" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
         <v>556</v>
       </c>
@@ -6358,10 +9253,20 @@
       <c r="C292" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D292" s="3"/>
-      <c r="E292" s="3"/>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D292" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>558</v>
       </c>
@@ -6371,10 +9276,20 @@
       <c r="C293" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D293" s="3"/>
-      <c r="E293" s="3"/>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D293" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
         <v>560</v>
       </c>
@@ -6384,10 +9299,20 @@
       <c r="C294" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D294" s="3"/>
-      <c r="E294" s="3"/>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D294" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>562</v>
       </c>
@@ -6397,10 +9322,20 @@
       <c r="C295" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D295" s="3"/>
-      <c r="E295" s="3"/>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D295" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
         <v>564</v>
       </c>
@@ -6410,10 +9345,20 @@
       <c r="C296" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="D296" s="3"/>
-      <c r="E296" s="3"/>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D296" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>567</v>
       </c>
@@ -6423,10 +9368,20 @@
       <c r="C297" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D297" s="3"/>
-      <c r="E297" s="3"/>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D297" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
         <v>569</v>
       </c>
@@ -6436,10 +9391,20 @@
       <c r="C298" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D298" s="3"/>
-      <c r="E298" s="3"/>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D298" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
         <v>571</v>
       </c>
@@ -6449,10 +9414,20 @@
       <c r="C299" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D299" s="3"/>
-      <c r="E299" s="3"/>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D299" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>571</v>
       </c>
@@ -6462,10 +9437,20 @@
       <c r="C300" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D300" s="3"/>
-      <c r="E300" s="3"/>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D300" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>571</v>
       </c>
@@ -6475,10 +9460,20 @@
       <c r="C301" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D301" s="3"/>
-      <c r="E301" s="3"/>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D301" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>575</v>
       </c>
@@ -6488,10 +9483,20 @@
       <c r="C302" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D302" s="3"/>
-      <c r="E302" s="3"/>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D302" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
         <v>577</v>
       </c>
@@ -6501,10 +9506,20 @@
       <c r="C303" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D303" s="3"/>
-      <c r="E303" s="3"/>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D303" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>579</v>
       </c>
@@ -6514,10 +9529,20 @@
       <c r="C304" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D304" s="3"/>
-      <c r="E304" s="3"/>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D304" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
         <v>581</v>
       </c>
@@ -6527,10 +9552,20 @@
       <c r="C305" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D305" s="3"/>
-      <c r="E305" s="3"/>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D305" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
         <v>583</v>
       </c>
@@ -6540,10 +9575,20 @@
       <c r="C306" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D306" s="3"/>
-      <c r="E306" s="3"/>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D306" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
         <v>585</v>
       </c>
@@ -6553,10 +9598,20 @@
       <c r="C307" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D307" s="3"/>
-      <c r="E307" s="3"/>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D307" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
         <v>587</v>
       </c>
@@ -6566,10 +9621,20 @@
       <c r="C308" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D308" s="3"/>
-      <c r="E308" s="3"/>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D308" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>589</v>
       </c>
@@ -6579,10 +9644,20 @@
       <c r="C309" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D309" s="3"/>
-      <c r="E309" s="3"/>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D309" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G309" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
         <v>591</v>
       </c>
@@ -6592,10 +9667,20 @@
       <c r="C310" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D310" s="3"/>
-      <c r="E310" s="3"/>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D310" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>593</v>
       </c>
@@ -6605,10 +9690,20 @@
       <c r="C311" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D311" s="3"/>
-      <c r="E311" s="3"/>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D311" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
         <v>595</v>
       </c>
@@ -6618,10 +9713,20 @@
       <c r="C312" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D312" s="3"/>
-      <c r="E312" s="3"/>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D312" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
         <v>597</v>
       </c>
@@ -6631,10 +9736,20 @@
       <c r="C313" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D313" s="3"/>
-      <c r="E313" s="3"/>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D313" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>599</v>
       </c>
@@ -6644,10 +9759,20 @@
       <c r="C314" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D314" s="3"/>
-      <c r="E314" s="3"/>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D314" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
         <v>601</v>
       </c>
@@ -6657,10 +9782,20 @@
       <c r="C315" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D315" s="3"/>
-      <c r="E315" s="3"/>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D315" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
         <v>603</v>
       </c>
@@ -6671,11 +9806,19 @@
         <v>2</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="E316" s="3"/>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>605</v>
       </c>
@@ -6685,10 +9828,20 @@
       <c r="C317" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="D317" s="3"/>
-      <c r="E317" s="3"/>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D317" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
         <v>608</v>
       </c>
@@ -6698,10 +9851,20 @@
       <c r="C318" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D318" s="3"/>
-      <c r="E318" s="3"/>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D318" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>610</v>
       </c>
@@ -6711,10 +9874,20 @@
       <c r="C319" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D319" s="3"/>
-      <c r="E319" s="3"/>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D319" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G319" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>612</v>
       </c>
@@ -6724,10 +9897,20 @@
       <c r="C320" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D320" s="3"/>
-      <c r="E320" s="3"/>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D320" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
         <v>614</v>
       </c>
@@ -6737,10 +9920,20 @@
       <c r="C321" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D321" s="3"/>
-      <c r="E321" s="3"/>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D321" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
         <v>616</v>
       </c>
@@ -6750,10 +9943,20 @@
       <c r="C322" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D322" s="3"/>
-      <c r="E322" s="3"/>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D322" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
         <v>618</v>
       </c>
@@ -6763,10 +9966,20 @@
       <c r="C323" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D323" s="3"/>
-      <c r="E323" s="3"/>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D323" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F323" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G323" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>620</v>
       </c>
@@ -6776,10 +9989,20 @@
       <c r="C324" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D324" s="3"/>
-      <c r="E324" s="3"/>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D324" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>622</v>
       </c>
@@ -6789,10 +10012,20 @@
       <c r="C325" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D325" s="3"/>
-      <c r="E325" s="3"/>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D325" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F325" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G325" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>624</v>
       </c>
@@ -6802,10 +10035,20 @@
       <c r="C326" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D326" s="3"/>
-      <c r="E326" s="3"/>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D326" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F326" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G326" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>626</v>
       </c>
@@ -6815,10 +10058,20 @@
       <c r="C327" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D327" s="3"/>
-      <c r="E327" s="3"/>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D327" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G327" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>628</v>
       </c>
@@ -6828,10 +10081,20 @@
       <c r="C328" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D328" s="3"/>
-      <c r="E328" s="3"/>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D328" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F328" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G328" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
         <v>630</v>
       </c>
@@ -6841,10 +10104,20 @@
       <c r="C329" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D329" s="3"/>
-      <c r="E329" s="3"/>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D329" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G329" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
         <v>630</v>
       </c>
@@ -6854,10 +10127,20 @@
       <c r="C330" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D330" s="3"/>
-      <c r="E330" s="3"/>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D330" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F330" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G330" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
         <v>633</v>
       </c>
@@ -6867,10 +10150,20 @@
       <c r="C331" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D331" s="3"/>
-      <c r="E331" s="3"/>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D331" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F331" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G331" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>635</v>
       </c>
@@ -6880,10 +10173,20 @@
       <c r="C332" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D332" s="3"/>
-      <c r="E332" s="3"/>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D332" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>637</v>
       </c>
@@ -6894,11 +10197,19 @@
         <v>2</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="E333" s="3"/>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+        <v>641</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F333" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G333" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
         <v>639</v>
       </c>
@@ -6908,12 +10219,22 @@
       <c r="C334" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D334" s="3"/>
-      <c r="E334" s="3"/>
+      <c r="D334" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F334" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G334" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H1:H33">
-    <sortCondition ref="H1:H33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G1:G33">
+    <sortCondition ref="G1:G33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
